--- a/education_forms/042_school_safety_plan_assessment_form--education_forms.xlsx
+++ b/education_forms/042_school_safety_plan_assessment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,158 +515,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>school_safety_plan_assessment_form</t>
+          <t>school_safety_plan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>school_safety_plan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>School Safety Plan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>review_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Review Frequency</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>assessment_date</t>
+          <t>review_protocol</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_of_assessment</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Review Protocol</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>review_frequency</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>review_frequency</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assessment_protocol</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>assessment_protocol</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Review Status</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>review_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Review Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -678,83 +658,71 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>safety_measures</t>
+          <t>review_responsible</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>safety_measures</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Review Responsible</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>review_due_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>review_status</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Review Due Date</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>review_comments</t>
+          <t>review_completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>review_comments</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Review Completed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -764,17 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_person</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Contact Person</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,22 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_details</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -813,369 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Contact Phone</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>contact_extension</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>contact_extension</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>review_responsible</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>review_responsible</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>review_due_date</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>review_due_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>review_completed</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>review_completed</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>review_frequency_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>review_frequency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>review_protocol</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>review_protocol</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>review_status_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>review_status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>review_comments_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>review_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact_person_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>contact_person</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_details_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contact_details</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>contact_email_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>contact_phone_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1190,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1218,357 +827,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>school_safety_plan_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>frequent</t>
+          <t>locking_doors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frequent</t>
+          <t>Locking doors</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>school_safety_plan_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>less_frequent</t>
+          <t>conducting_drills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Less frequent</t>
+          <t>Conducting drills</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>review_frequency_choices</t>
+          <t>school_safety_plan_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>emergency_exit_plan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Emergency exit plan</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assessment_protocol_choices</t>
+          <t>school_safety_plan_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>locking_doors</t>
+          <t>first_aid_kit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Locking doors</t>
+          <t>First aid kit</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>assessment_protocol_choices</t>
+          <t>school_safety_plan_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>conducting_drills</t>
+          <t>safety_protocols</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Conducting drills</t>
+          <t>Safety protocols</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assessment_protocol_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emergency_exit_plan</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emergency exit plan</t>
+          <t>Frequent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assessment_protocol_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_aid_kit</t>
+          <t>less_frequent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>First aid kit</t>
+          <t>Less frequent</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assessment_protocol_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>safety_protocols</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Safety protocols</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emergency_exits</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emergency exits</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>review_protocol_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>secure_doors</t>
+          <t>review_protocols</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Secure doors</t>
+          <t>Review protocols</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>review_protocol_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>safety_protocols</t>
+          <t>conducting_drills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Safety protocols</t>
+          <t>Conducting drills</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>review_protocol_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_aid_kits</t>
+          <t>locking_doors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First aid kits</t>
+          <t>Locking doors</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>safety_measures_choices</t>
+          <t>review_protocol_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>security_cameras</t>
+          <t>safety_measures</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Security cameras</t>
+          <t>Safety measures</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>review_status_choices</t>
+          <t>contact_information_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Principal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>review_status_choices</t>
+          <t>contact_information_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>facilities_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Facilities manager</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>review_status_choices</t>
+          <t>contact_information_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>security_officer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Security officer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>contact_information_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>safety_officer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Safety officer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>contact_information_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>facilities_manager</t>
+          <t>maintenance_staff</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Facilities manager</t>
+          <t>Maintenance staff</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>review_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>security_officer</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Security officer</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>review_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>safety_officer</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Safety officer</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>review_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>maintenance_staff</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Maintenance staff</t>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -1654,261 +1263,6 @@
       <c r="C27" t="inlineStr">
         <is>
           <t>Not completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>review_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>frequent</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Frequent</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>review_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>less_frequent</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Less frequent</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>review_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>review_protocol_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>review_protocols</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Review protocols</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>review_protocol_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>conducting_drills</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Conducting drills</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>review_protocol_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>locking_doors</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Locking doors</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>review_protocol_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>safety_measures</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Safety measures</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>review_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>review_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>review_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>not_started</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>principal</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>facilities_manager</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Facilities manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>security_officer</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Security officer</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>safety_officer</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Safety officer</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>contact_person_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>maintenance_staff</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Maintenance staff</t>
         </is>
       </c>
     </row>
